--- a/data/hex_xlsx/TRH1V.HE.xlsx
+++ b/data/hex_xlsx/TRH1V.HE.xlsx
@@ -10387,14 +10387,38 @@
       <c r="O50" s="15">
         <v>2.79</v>
       </c>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="20"/>
-      <c r="R50" s="20"/>
-      <c r="S50" s="20"/>
-      <c r="T50" s="20"/>
-      <c r="U50" s="20"/>
-      <c r="V50" s="20"/>
-      <c r="W50" s="20"/>
+      <c r="P50" s="15">
+        <f>SUM(P51,P54)</f>
+        <v>4.59</v>
+      </c>
+      <c r="Q50" s="15">
+        <f t="shared" ref="Q50:W50" si="1">SUM(Q53,Q55,Q48)</f>
+        <v>8.03</v>
+      </c>
+      <c r="R50" s="15">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="S50" s="15">
+        <f t="shared" si="1"/>
+        <v>7.58</v>
+      </c>
+      <c r="T50" s="15">
+        <f t="shared" si="1"/>
+        <v>13.52</v>
+      </c>
+      <c r="U50" s="15">
+        <f t="shared" si="1"/>
+        <v>13.09</v>
+      </c>
+      <c r="V50" s="15">
+        <f t="shared" si="1"/>
+        <v>9.19</v>
+      </c>
+      <c r="W50" s="15">
+        <f t="shared" si="1"/>
+        <v>11.56</v>
+      </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
@@ -11277,15 +11301,9 @@
       <c r="J69" s="20"/>
       <c r="K69" s="20"/>
       <c r="L69" s="20"/>
-      <c r="M69" s="15">
-        <v>0.25</v>
-      </c>
-      <c r="N69" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="O69" s="15">
-        <v>1.0</v>
-      </c>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
       <c r="P69" s="15">
         <v>1.54</v>
       </c>
